--- a/EXCEL/Data/løn_data/løn_klassificering.xlsx
+++ b/EXCEL/Data/løn_data/løn_klassificering.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="50">
   <si>
     <t xml:space="preserve">Lønniveau - feb 2025 </t>
   </si>
@@ -31,6 +31,18 @@
     <t>Fuldtid</t>
   </si>
   <si>
+    <t>Lokale tillæg</t>
+  </si>
+  <si>
+    <t>Særydelser</t>
+  </si>
+  <si>
+    <t>Overarbejde</t>
+  </si>
+  <si>
+    <t>Nettoløn</t>
+  </si>
+  <si>
     <t>Bruttoløn</t>
   </si>
   <si>
@@ -88,7 +100,7 @@
     <t>Datasæt 02 2025</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 14.25.34</t>
+    <t>Kørsel 10.4.2026 10.34.28</t>
   </si>
   <si>
     <t/>
@@ -140,9 +152,6 @@
   </si>
   <si>
     <t>Lokalt aftalte tillæg</t>
-  </si>
-  <si>
-    <t>Særydelser</t>
   </si>
   <si>
     <t>Feriegodtgørelse</t>
@@ -600,18 +609,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="10" width="10" customWidth="1"/>
+    <col min="5" max="10" width="18" customWidth="1"/>
+    <col min="11" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,8 +629,12 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -640,979 +653,1483 @@
       <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5">
-        <v>1498.4778681553187</v>
+        <v>1498.477868155319</v>
       </c>
       <c r="F3" s="6">
-        <v>53109.454098413014</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16011.426210719794</v>
+      </c>
+      <c r="G3" s="6">
+        <v>441.049958296305</v>
+      </c>
+      <c r="H3" s="6">
+        <v>158.09423046762709</v>
+      </c>
+      <c r="I3" s="6">
+        <v>43545.49182730396</v>
+      </c>
+      <c r="J3" s="6">
+        <v>53113.390644837455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" s="8">
-        <v>372.9944409998168</v>
+        <v>372.99444099981685</v>
       </c>
       <c r="F4" s="9">
-        <v>50774.40335862347</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10679.360878629619</v>
+      </c>
+      <c r="G4" s="9">
+        <v>250.22665378998607</v>
+      </c>
+      <c r="H4" s="9">
+        <v>91.95363963843495</v>
+      </c>
+      <c r="I4" s="9">
+        <v>41671.86121897748</v>
+      </c>
+      <c r="J4" s="9">
+        <v>50776.693004300345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5">
         <v>53.670100000000005</v>
       </c>
       <c r="F5" s="6">
+        <v>39707.512190213914</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>44089.86661101806</v>
+      </c>
+      <c r="J5" s="6">
         <v>52816.61182301361</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" s="8">
         <v>14.7351</v>
       </c>
       <c r="F6" s="9">
+        <v>42439.14191284755</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>45154.5547705818</v>
+      </c>
+      <c r="J6" s="9">
         <v>54142.9721429899</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5">
-        <v>7.437799999999999</v>
+        <v>7.4378</v>
       </c>
       <c r="F7" s="6">
+        <v>45322.27809298448</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>45322.27809298448</v>
+      </c>
+      <c r="J7" s="6">
         <v>54254.93712910306</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E8" s="8">
         <v>6.2973</v>
       </c>
       <c r="F8" s="9">
-        <v>55000.17017001334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45773.102758325</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>45773.102758325</v>
+      </c>
+      <c r="J8" s="9">
+        <v>55000.17017001336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E9" s="5">
         <v>27.8242</v>
       </c>
       <c r="F9" s="6">
-        <v>51494.14921019934</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37386.40428116532</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>42948.960257617466</v>
+      </c>
+      <c r="J9" s="6">
+        <v>51494.149210199335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" s="8">
         <v>19.1756</v>
       </c>
       <c r="F10" s="9">
+        <v>41413.94636934439</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>43963.12292705313</v>
+      </c>
+      <c r="J10" s="9">
         <v>52679.01601933469</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E11" s="5">
         <v>11.110800000000001</v>
       </c>
       <c r="F11" s="6">
+        <v>41897.46552903481</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45534.993879828624</v>
+      </c>
+      <c r="J11" s="6">
         <v>54369.372405562506</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E12" s="8">
         <v>7.1108</v>
       </c>
       <c r="F12" s="9">
+        <v>47638.48793384711</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>47638.48793384711</v>
+      </c>
+      <c r="J12" s="9">
         <v>57033.12369066308</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5">
         <v>319.32434099981685</v>
       </c>
       <c r="F13" s="6">
-        <v>50431.161336541816</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5800.485128569749</v>
+      </c>
+      <c r="G13" s="6">
+        <v>292.28323328381686</v>
+      </c>
+      <c r="H13" s="6">
+        <v>107.40865011244576</v>
+      </c>
+      <c r="I13" s="6">
+        <v>41265.45752677842</v>
+      </c>
+      <c r="J13" s="6">
+        <v>50433.83581198787</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E14" s="8">
         <v>47.66610642545228</v>
       </c>
       <c r="F14" s="9">
-        <v>49696.40893752927</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5843.222999962125</v>
+      </c>
+      <c r="G14" s="9">
+        <v>391.1497701271865</v>
+      </c>
+      <c r="H14" s="9">
+        <v>190.71984278143375</v>
+      </c>
+      <c r="I14" s="9">
+        <v>40563.35018637696</v>
+      </c>
+      <c r="J14" s="9">
+        <v>49701.15786171798</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E15" s="5">
         <v>18.150929819089207</v>
       </c>
       <c r="F15" s="6">
-        <v>49218.14229678242</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5992.123560408845</v>
+      </c>
+      <c r="G15" s="6">
+        <v>794.7224317433769</v>
+      </c>
+      <c r="H15" s="6">
+        <v>500.84884984264227</v>
+      </c>
+      <c r="I15" s="6">
+        <v>39822.04066170251</v>
+      </c>
+      <c r="J15" s="6">
+        <v>49230.613433415165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E16" s="8">
         <v>10.985476606363068</v>
       </c>
       <c r="F16" s="9">
-        <v>46647.96072299413</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3576.559905356809</v>
+      </c>
+      <c r="G16" s="9">
+        <v>349.05184030934953</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>38064.48175780233</v>
+      </c>
+      <c r="J16" s="9">
+        <v>46647.96072299414</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="E17" s="5">
         <v>12.2027</v>
       </c>
       <c r="F17" s="6">
-        <v>52060.57766423818</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7173.441123685742</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <v>42830.635971205826</v>
+      </c>
+      <c r="J17" s="6">
+        <v>52060.57766423817</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" s="8">
         <v>210.14746666252165</v>
       </c>
       <c r="F18" s="9">
-        <v>49822.802949033125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5379.088170839237</v>
+      </c>
+      <c r="G18" s="9">
+        <v>34.54701998629103</v>
+      </c>
+      <c r="H18" s="9">
+        <v>18.911979431817404</v>
+      </c>
+      <c r="I18" s="9">
+        <v>41004.9900956848</v>
+      </c>
+      <c r="J18" s="9">
+        <v>49823.27385733128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5">
-        <v>12.8108</v>
+        <v>12.810800000000002</v>
       </c>
       <c r="F19" s="6">
+        <v>4154.533674711961</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6">
+        <v>40542.439955285125</v>
+      </c>
+      <c r="J19" s="6">
         <v>49285.65692301952</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E20" s="8">
         <v>58.33860220525406</v>
       </c>
       <c r="F20" s="9">
-        <v>49858.18934099003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5312.601715316278</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>41042.87261126631</v>
+      </c>
+      <c r="J20" s="9">
+        <v>49858.18934099004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5">
         <v>34.449851606363076</v>
       </c>
       <c r="F21" s="6">
-        <v>48117.37424651774</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4107.233060074482</v>
+      </c>
+      <c r="G21" s="6">
+        <v>6.119819050634466</v>
+      </c>
+      <c r="H21" s="6">
+        <v>115.36492559045065</v>
+      </c>
+      <c r="I21" s="6">
+        <v>39583.491516021146</v>
+      </c>
+      <c r="J21" s="6">
+        <v>48120.246833227524</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="E22" s="8">
         <v>86.89151285090456</v>
       </c>
       <c r="F22" s="9">
-        <v>50088.7127777082</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5723.177997054803</v>
+      </c>
+      <c r="G22" s="9">
+        <v>81.12578134992191</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>41225.701052605786</v>
+      </c>
+      <c r="J22" s="9">
+        <v>50088.71277770819</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E23" s="5">
         <v>15.4</v>
       </c>
       <c r="F23" s="6">
+        <v>6297.348051948052</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6">
+        <v>41672.87399891775</v>
+      </c>
+      <c r="J23" s="6">
         <v>50604.13053214621</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E24" s="8">
         <v>61.5107679118431</v>
       </c>
       <c r="F24" s="9">
-        <v>53078.95400007904</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7207.04138103226</v>
+      </c>
+      <c r="G24" s="9">
+        <v>1096.2079948059932</v>
+      </c>
+      <c r="H24" s="9">
+        <v>345.1919110265735</v>
+      </c>
+      <c r="I24" s="9">
+        <v>42699.40636202136</v>
+      </c>
+      <c r="J24" s="9">
+        <v>53087.549278850835</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E25" s="5">
-        <v>9.405500000000002</v>
+        <v>9.4055</v>
       </c>
       <c r="F25" s="6">
+        <v>5848.451437988412</v>
+      </c>
+      <c r="G25" s="6">
+        <v>386.58371134710796</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6">
+        <v>40494.8221799922</v>
+      </c>
+      <c r="J25" s="6">
         <v>49655.60142264217</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E26" s="8">
         <v>19.844444143907978</v>
       </c>
       <c r="F26" s="9">
-        <v>53043.095424606996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7497.663515975369</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1405.1459813722252</v>
+      </c>
+      <c r="H26" s="9">
+        <v>394.8546969291222</v>
+      </c>
+      <c r="I26" s="9">
+        <v>42397.700611107946</v>
+      </c>
+      <c r="J26" s="9">
+        <v>53052.9273067747</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="E27" s="5">
         <v>20.922266063630694</v>
       </c>
       <c r="F27" s="6">
-        <v>54127.1010945752</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8039.225032357991</v>
+      </c>
+      <c r="G27" s="6">
+        <v>146.56665239985813</v>
+      </c>
+      <c r="H27" s="6">
+        <v>171.42255225890997</v>
+      </c>
+      <c r="I27" s="6">
+        <v>44410.32282031721</v>
+      </c>
+      <c r="J27" s="6">
+        <v>54131.36951621942</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E28" s="8">
         <v>6.9189</v>
       </c>
       <c r="F28" s="9">
-        <v>54362.07845105378</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6693.241700270274</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3284.8485030243232</v>
+      </c>
+      <c r="H28" s="9">
+        <v>1417.9709633560137</v>
+      </c>
+      <c r="I28" s="9">
+        <v>41886.47703548734</v>
+      </c>
+      <c r="J28" s="9">
+        <v>54397.385928810465</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E29" s="5">
         <v>1125.483427155501</v>
       </c>
       <c r="F29" s="6">
-        <v>53883.309069867864</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17778.51640496991</v>
+      </c>
+      <c r="G29" s="6">
+        <v>504.2903668858477</v>
+      </c>
+      <c r="H29" s="6">
+        <v>180.01376487257377</v>
+      </c>
+      <c r="I29" s="6">
+        <v>44166.42838179348</v>
+      </c>
+      <c r="J29" s="6">
+        <v>53887.791412710874</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E30" s="8">
-        <v>283.8057004990643</v>
+        <v>283.80570049906424</v>
       </c>
       <c r="F30" s="9">
-        <v>55558.8664043747</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46337.07962672847</v>
+      </c>
+      <c r="G30" s="9">
+        <v>389.6525121539717</v>
+      </c>
+      <c r="H30" s="9">
+        <v>54.64648968181533</v>
+      </c>
+      <c r="I30" s="9">
+        <v>46453.34427981731</v>
+      </c>
+      <c r="J30" s="9">
+        <v>55560.22710199744</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E31" s="5">
-        <v>283.8057004990643</v>
+        <v>283.80570049906424</v>
       </c>
       <c r="F31" s="6">
-        <v>55558.8664043747</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46337.07962672847</v>
+      </c>
+      <c r="G31" s="6">
+        <v>389.6525121539717</v>
+      </c>
+      <c r="H31" s="6">
+        <v>54.64648968181533</v>
+      </c>
+      <c r="I31" s="6">
+        <v>46453.34427981731</v>
+      </c>
+      <c r="J31" s="6">
+        <v>55560.22710199744</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E32" s="8">
-        <v>19.290032127261387</v>
+        <v>19.290032127261384</v>
       </c>
       <c r="F32" s="9">
+        <v>41115.680615126075</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>41691.149848498266</v>
+      </c>
+      <c r="J32" s="9">
         <v>50828.887989662384</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E33" s="5">
-        <v>59.36769794135994</v>
+        <v>59.36769794135995</v>
       </c>
       <c r="F33" s="6">
-        <v>52218.00831156999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43219.41782345972</v>
+      </c>
+      <c r="G33" s="6">
+        <v>881.9026157266712</v>
+      </c>
+      <c r="H33" s="6">
+        <v>150.42430123648836</v>
+      </c>
+      <c r="I33" s="6">
+        <v>43387.240253142</v>
+      </c>
+      <c r="J33" s="6">
+        <v>52221.75387675236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E34" s="8">
         <v>110.52730000000001</v>
       </c>
       <c r="F34" s="9">
-        <v>58953.402290742655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49034.45546937274</v>
+      </c>
+      <c r="G34" s="9">
+        <v>411.51521565060534</v>
+      </c>
+      <c r="H34" s="9">
+        <v>56.21692031513565</v>
+      </c>
+      <c r="I34" s="9">
+        <v>48985.551985799</v>
+      </c>
+      <c r="J34" s="9">
+        <v>58954.802092089</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E35" s="5">
-        <v>94.62067043044291</v>
+        <v>94.62067043044293</v>
       </c>
       <c r="F35" s="6">
-        <v>54654.11275821818</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46206.82996760218</v>
+      </c>
+      <c r="G35" s="6">
+        <v>134.70006401520902</v>
+      </c>
+      <c r="H35" s="6">
+        <v>3.8589494949291416</v>
+      </c>
+      <c r="I35" s="6">
+        <v>46390.0636090584</v>
+      </c>
+      <c r="J35" s="6">
+        <v>54654.208846062706</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E36" s="8">
         <v>841.6777266564355</v>
       </c>
       <c r="F36" s="9">
-        <v>53318.32712014339</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8148.841312348065</v>
+      </c>
+      <c r="G36" s="9">
+        <v>542.9451579483788</v>
+      </c>
+      <c r="H36" s="9">
+        <v>222.28641416378613</v>
+      </c>
+      <c r="I36" s="9">
+        <v>43395.30215632077</v>
+      </c>
+      <c r="J36" s="9">
+        <v>53323.862051976546</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E37" s="5">
         <v>841.6777266564355</v>
       </c>
       <c r="F37" s="6">
-        <v>53318.32712014339</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8148.841312348065</v>
+      </c>
+      <c r="G37" s="6">
+        <v>542.9451579483788</v>
+      </c>
+      <c r="H37" s="6">
+        <v>222.28641416378613</v>
+      </c>
+      <c r="I37" s="6">
+        <v>43395.30215632077</v>
+      </c>
+      <c r="J37" s="6">
+        <v>53323.862051976546</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E38" s="8">
         <v>46.34384273237679</v>
       </c>
       <c r="F38" s="9">
-        <v>51577.01939385992</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6392.854995438814</v>
+      </c>
+      <c r="G38" s="9">
+        <v>55.45329630014375</v>
+      </c>
+      <c r="H38" s="9">
+        <v>10.61664232144989</v>
+      </c>
+      <c r="I38" s="9">
+        <v>42243.97302575852</v>
+      </c>
+      <c r="J38" s="9">
+        <v>51577.28374825947</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="5">
+        <v>185.27698519768384</v>
+      </c>
+      <c r="F39" s="6">
+        <v>6106.4448244519435</v>
+      </c>
+      <c r="G39" s="6">
+        <v>313.7836868631895</v>
+      </c>
+      <c r="H39" s="6">
+        <v>5.933211215928379</v>
+      </c>
+      <c r="I39" s="6">
+        <v>41572.245258803734</v>
+      </c>
+      <c r="J39" s="6">
+        <v>50889.44036498493</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="8">
+        <v>179.84211107709118</v>
+      </c>
+      <c r="F40" s="9">
+        <v>7425.967697827587</v>
+      </c>
+      <c r="G40" s="9">
+        <v>871.4563768792351</v>
+      </c>
+      <c r="H40" s="9">
+        <v>442.75101704180065</v>
+      </c>
+      <c r="I40" s="9">
+        <v>42637.51238120964</v>
+      </c>
+      <c r="J40" s="9">
+        <v>52729.13413658939</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="E41" s="5">
+        <v>339.9580302781238</v>
+      </c>
+      <c r="F41" s="6">
+        <v>9566.740367605127</v>
+      </c>
+      <c r="G41" s="6">
+        <v>516.7956516584878</v>
+      </c>
+      <c r="H41" s="6">
+        <v>246.5140127091358</v>
+      </c>
+      <c r="I41" s="6">
+        <v>44683.16610280975</v>
+      </c>
+      <c r="J41" s="6">
+        <v>54839.59528762453</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="5">
-        <v>185.27698519768393</v>
-      </c>
-      <c r="F39" s="6">
-        <v>50889.29262802241</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="8">
-        <v>179.84211107709123</v>
-      </c>
-      <c r="F40" s="9">
-        <v>52718.10963602484</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="5">
-        <v>339.95803027812383</v>
-      </c>
-      <c r="F41" s="6">
-        <v>54833.45708857427</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="E42" s="8">
-        <v>87.4926467036613</v>
+        <v>87.49264670366128</v>
       </c>
       <c r="F42" s="9">
-        <v>54746.588029244755</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9326.809389561146</v>
+      </c>
+      <c r="G42" s="9">
+        <v>728.7605296257947</v>
+      </c>
+      <c r="H42" s="9">
+        <v>216.25097206534997</v>
+      </c>
+      <c r="I42" s="9">
+        <v>44418.1695018525</v>
+      </c>
+      <c r="J42" s="9">
+        <v>54751.97267856647</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>30</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A45:J45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
